--- a/public/templates/champion-import-players.xlsx
+++ b/public/templates/champion-import-players.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гравці" sheetId="1" r:id="Rcd7bfa14d32841d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інструкція" sheetId="2" r:id="R3c04e7c291744ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гравці" sheetId="1" r:id="Rf9d339c537614513"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інструкція" sheetId="2" r:id="R303e9afd2ada4cc7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16098,7 +16098,7 @@
   </x:sheetData>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="A2:A5001">
-      <x:formula1>"U6,U7,U8A,U8B,U9A,U9B,U10A,U10B,U11A,U11B,U12A,U12B,U13A,U13B,U14A,U14B,U15A,U15B,Воротарі A,Воротарі B,Воротарі C"</x:formula1>
+      <x:formula1>"U6,U7,U8A,U8B,U9A,U9B,U10A,U10B,U11A,U11B,U12A,U12B,U13A,U13B,U14A,U14B,U15A,U15B,U16A,U16B,U17A,U17B,Воротарі A,Воротарі B,Воротарі C"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="whole" operator="between" sqref="C2:C5001">
       <x:formula1>2000</x:formula1>
